--- a/LubanConfig/MiniTemplate/Datas/level/10020.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/level/10020.xlsx
@@ -713,10 +713,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2003</v>
+        <v>2037</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>1</v>
@@ -726,17 +726,17 @@
         <v>0.7</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>25.3</v>
+        <v>18.2</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-3.4</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>绿蝙蝠</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -756,10 +756,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2004</v>
+        <v>2035</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>1</v>
@@ -769,17 +769,17 @@
         <v>0.6</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>25.3</v>
+        <v>18.2</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-3.4</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>绿蝾螈</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -788,10 +788,10 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2008</v>
+        <v>2001</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>1</v>
@@ -812,17 +812,17 @@
         <v>0.5</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>25.3</v>
+        <v>18.2</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-3.4</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>黄鹿角</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="O9" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -842,10 +842,10 @@
         <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2002</v>
+        <v>2009</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>1</v>
@@ -855,17 +855,17 @@
         <v>0.7</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>23.1</v>
+        <v>18.3</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>萨哈比精英坦克</t>
+          <t>精英黄电兔</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -874,10 +874,10 @@
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -885,30 +885,30 @@
         <v>2</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2005</v>
+        <v>2014</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>23.1</v>
+        <v>18.3</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>刘易斯</t>
+          <t>精英蜗牛</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -917,37 +917,53 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="D12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="n">
+        <v>2044</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>1.2</v>
+      </c>
       <c r="K12" s="2" t="n">
-        <v>23.1</v>
+        <v>18.3</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>精英绿花</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="n">
+        <v>3.6</v>
+      </c>
       <c r="P12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -955,42 +971,42 @@
         <v>3</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>27.9</v>
+        <v>11.5</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-5.9</v>
+        <v>0.2</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>蜗牛</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -998,69 +1014,85 @@
         <v>3</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2003</v>
+        <v>2024</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>27.9</v>
+        <v>11.5</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-5.9</v>
+        <v>0.2</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>黄蝾螈</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O14" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="D15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="n">
+        <v>2003</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K15" s="2" t="n">
-        <v>27.9</v>
+        <v>11.5</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-5.9</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>黄树怪</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr"/>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>3.6</v>
+      </c>
       <c r="P15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1068,30 +1100,30 @@
         <v>4</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2002</v>
+        <v>2009</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>21.4</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>萨哈比精英坦克</t>
+          <t>精英黄电兔</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1100,10 +1132,10 @@
         </is>
       </c>
       <c r="O16" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1111,30 +1143,30 @@
         <v>4</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2007</v>
+        <v>2029</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>21.4</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>垃圾刺客</t>
+          <t>精英粉蝾螈</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1143,53 +1175,37 @@
         </is>
       </c>
       <c r="O17" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="D18" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E18" s="2" t="n">
-        <v>2006</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>4</v>
-      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="n">
         <v>21.4</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>精射手</t>
-        </is>
-      </c>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O18" s="2" t="n">
-        <v>3.2</v>
-      </c>
+      <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1197,30 +1213,30 @@
         <v>5</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2004</v>
+        <v>2038</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>16.7</v>
+        <v>15.7</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-7.4</v>
+        <v>-9.5</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>绿花</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1229,10 +1245,10 @@
         </is>
       </c>
       <c r="O19" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1240,30 +1256,30 @@
         <v>5</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>1.2</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>16.7</v>
+        <v>15.7</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-7.4</v>
+        <v>-9.5</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>粉蝙蝠</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1272,10 +1288,10 @@
         </is>
       </c>
       <c r="O20" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1283,13 +1299,13 @@
         <v>5</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2008</v>
+        <v>2037</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="n">
@@ -1299,14 +1315,14 @@
         <v>1.1</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>16.7</v>
+        <v>15.7</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-7.4</v>
+        <v>-9.5</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>绿蝙蝠</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -1315,10 +1331,10 @@
         </is>
       </c>
       <c r="O21" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1326,30 +1342,30 @@
         <v>6</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2002</v>
+        <v>2042</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>萨哈比精英坦克</t>
+          <t>精英绿兔子</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -1358,10 +1374,10 @@
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1369,30 +1385,30 @@
         <v>6</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>2006</v>
+        <v>2013</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>精射手</t>
+          <t>精英绿皮怪1</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -1401,53 +1417,37 @@
         </is>
       </c>
       <c r="O23" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="D24" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E24" s="2" t="n">
-        <v>2007</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>2</v>
-      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>垃圾刺客</t>
-        </is>
-      </c>
+        <v>6.2</v>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O24" s="2" t="n">
-        <v>3.2</v>
-      </c>
+      <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1455,30 +1455,30 @@
         <v>7</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2004</v>
+        <v>2040</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>17</v>
+        <v>20.5</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>-9.300000000000001</v>
+        <v>-7.9</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>绿蘑菇</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="O25" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1498,30 +1498,30 @@
         <v>7</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2003</v>
+        <v>2027</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>11</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>17</v>
+        <v>20.5</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>-9.300000000000001</v>
+        <v>-7.9</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>黄战士</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="O26" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1547,10 +1547,10 @@
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="n">
-        <v>17</v>
+        <v>20.5</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>-9.300000000000001</v>
+        <v>-7.9</v>
       </c>
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1568,30 +1568,30 @@
         <v>8</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>2004</v>
+        <v>2028</v>
       </c>
       <c r="F28" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G28" s="2" t="n">
         <v>6</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>2</v>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>22</v>
+        <v>19.6</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>-7.9</v>
+        <v>-4.1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>黄犀牛</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="O28" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1611,30 +1611,30 @@
         <v>8</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>2003</v>
+        <v>2026</v>
       </c>
       <c r="F29" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G29" s="2" t="n">
         <v>6</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>2</v>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>22</v>
+        <v>19.6</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>-7.9</v>
+        <v>-4.1</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>紫蝙蝠</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -1643,53 +1643,37 @@
         </is>
       </c>
       <c r="O29" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="D30" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E30" s="2" t="n">
-        <v>2008</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>2</v>
-      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="n">
-        <v>22</v>
+        <v>19.6</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>-7.9</v>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>影流之主</t>
-        </is>
-      </c>
+        <v>-4.1</v>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>轻松</t>
         </is>
       </c>
-      <c r="O30" s="2" t="n">
-        <v>3.2</v>
-      </c>
+      <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1697,30 +1681,30 @@
         <v>9</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>10.7</v>
+        <v>12.7</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>-3.7</v>
+        <v>-5</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>岩石龟</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -1729,10 +1713,10 @@
         </is>
       </c>
       <c r="O31" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1740,30 +1724,30 @@
         <v>9</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>2003</v>
+        <v>2040</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>10.7</v>
+        <v>12.7</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>-3.7</v>
+        <v>-5</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>绿蘑菇</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -1772,53 +1756,37 @@
         </is>
       </c>
       <c r="O32" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="D33" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E33" s="2" t="n">
-        <v>2008</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>3</v>
-      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="n">
-        <v>10.7</v>
+        <v>12.7</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>影流之主</t>
-        </is>
-      </c>
+        <v>-5</v>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="O33" s="2" t="n">
-        <v>3.2</v>
-      </c>
+      <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -1826,42 +1794,42 @@
         <v>10</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>2001</v>
+        <v>2040</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J34" s="2" t="n">
-        <v>1.1</v>
-      </c>
       <c r="K34" s="2" t="n">
-        <v>12</v>
+        <v>21.2</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>6.4</v>
+        <v>-8.1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>普通坦克</t>
+          <t>绿蘑菇</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O34" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -1869,42 +1837,42 @@
         <v>10</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>2004</v>
+        <v>2037</v>
       </c>
       <c r="F35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G35" s="2" t="n">
         <v>7</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>3</v>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J35" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="J35" s="2" t="n">
-        <v>1.1</v>
-      </c>
       <c r="K35" s="2" t="n">
-        <v>12</v>
+        <v>21.2</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>6.4</v>
+        <v>-8.1</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>绿蝙蝠</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O35" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1912,42 +1880,42 @@
         <v>10</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>2008</v>
+        <v>2003</v>
       </c>
       <c r="F36" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G36" s="2" t="n">
         <v>7</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>5</v>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>12</v>
+        <v>21.2</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>6.4</v>
+        <v>-8.1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>黄树怪</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O36" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -1955,30 +1923,30 @@
         <v>11</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>2004</v>
+        <v>2039</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>11.9</v>
+        <v>6.4</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>-0.4</v>
+        <v>3.6</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>绿螃蟹</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -1987,10 +1955,10 @@
         </is>
       </c>
       <c r="O37" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P37" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -1998,30 +1966,30 @@
         <v>11</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>2008</v>
+        <v>2028</v>
       </c>
       <c r="F38" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G38" s="2" t="n">
         <v>8</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>3</v>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>11.9</v>
+        <v>6.4</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>-0.4</v>
+        <v>3.6</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>黄犀牛</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -2030,37 +1998,53 @@
         </is>
       </c>
       <c r="O38" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="D39" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K39" s="2" t="n">
-        <v>11.9</v>
+        <v>6.4</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+        <v>3.6</v>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>黄蝾螈</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="O39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="n">
+        <v>3.6</v>
+      </c>
       <c r="P39" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2068,13 +2052,13 @@
         <v>12</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>2003</v>
+        <v>2027</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="n">
@@ -2084,14 +2068,14 @@
         <v>1.1</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>25.1</v>
+        <v>20</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>-8.699999999999999</v>
+        <v>-5.1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>黄战士</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -2100,10 +2084,10 @@
         </is>
       </c>
       <c r="O40" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2111,13 +2095,13 @@
         <v>12</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="n">
@@ -2127,14 +2111,14 @@
         <v>1.1</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>25.1</v>
+        <v>20</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>-8.699999999999999</v>
+        <v>-5.1</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>绿皮怪1</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -2143,53 +2127,37 @@
         </is>
       </c>
       <c r="O41" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P41" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="D42" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E42" s="2" t="n">
-        <v>2008</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>3</v>
-      </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="n">
-        <v>25.1</v>
+        <v>20</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>-8.699999999999999</v>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>影流之主</t>
-        </is>
-      </c>
+        <v>-5.1</v>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>轻松</t>
         </is>
       </c>
-      <c r="O42" s="2" t="n">
-        <v>3.2</v>
-      </c>
+      <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2197,30 +2165,30 @@
         <v>13</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>21.9</v>
+        <v>20.3</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>-8.300000000000001</v>
+        <v>-9.6</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>绿皮怪1</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -2229,10 +2197,10 @@
         </is>
       </c>
       <c r="O43" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P43" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2240,30 +2208,30 @@
         <v>13</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>21.9</v>
+        <v>20.3</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>-8.300000000000001</v>
+        <v>-9.6</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>蜗牛</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -2272,10 +2240,10 @@
         </is>
       </c>
       <c r="O44" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2289,10 +2257,10 @@
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="n">
-        <v>21.9</v>
+        <v>20.3</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>-8.300000000000001</v>
+        <v>-9.6</v>
       </c>
       <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
@@ -2302,7 +2270,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr"/>
       <c r="P45" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -2310,7 +2278,7 @@
         <v>14</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>2001</v>
+        <v>2039</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>2</v>
@@ -2320,20 +2288,20 @@
       </c>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>-2.2</v>
+        <v>1.1</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>普通坦克</t>
+          <t>绿螃蟹</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -2342,10 +2310,10 @@
         </is>
       </c>
       <c r="O46" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P46" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -2353,30 +2321,30 @@
         <v>14</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>2003</v>
+        <v>2023</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>-2.2</v>
+        <v>1.1</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>粉蝾螈</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -2385,37 +2353,53 @@
         </is>
       </c>
       <c r="O47" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P47" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="D48" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K48" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+        <v>1.1</v>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>紫蝙蝠</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="O48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="n">
+        <v>3.6</v>
+      </c>
       <c r="P48" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -2426,27 +2410,27 @@
         <v>2004</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>12.3</v>
+        <v>13.6</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>-0.8</v>
+        <v>-0.4</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>粉蝙蝠</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -2455,10 +2439,10 @@
         </is>
       </c>
       <c r="O49" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P49" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -2466,13 +2450,13 @@
         <v>15</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="n">
@@ -2482,14 +2466,14 @@
         <v>1.1</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>12.3</v>
+        <v>13.6</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>-0.8</v>
+        <v>-0.4</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>蜗牛</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -2498,37 +2482,53 @@
         </is>
       </c>
       <c r="O50" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P50" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="D51" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E51" s="2" t="inlineStr"/>
-      <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K51" s="2" t="n">
-        <v>12.3</v>
+        <v>13.6</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+        <v>-0.4</v>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>绿蘑菇</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="O51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="n">
+        <v>3.6</v>
+      </c>
       <c r="P51" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -2536,30 +2536,30 @@
         <v>16</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>2008</v>
+        <v>2035</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>15.3</v>
+        <v>25.3</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>-5</v>
+        <v>-6.3</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>绿蝾螈</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="O52" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P52" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -2579,30 +2579,30 @@
         <v>16</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>2004</v>
+        <v>2038</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>15.3</v>
+        <v>25.3</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>-5</v>
+        <v>-6.3</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>绿花</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -2611,37 +2611,53 @@
         </is>
       </c>
       <c r="O53" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P53" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="D54" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="n">
+        <v>2028</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K54" s="2" t="n">
-        <v>15.3</v>
+        <v>25.3</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>-5</v>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+        <v>-6.3</v>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>黄犀牛</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>轻松</t>
         </is>
       </c>
-      <c r="O54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="n">
+        <v>3.6</v>
+      </c>
       <c r="P54" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -2649,7 +2665,7 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>2001</v>
+        <v>2036</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>2</v>
@@ -2659,20 +2675,20 @@
       </c>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J55" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J55" s="2" t="n">
-        <v>1.1</v>
-      </c>
       <c r="K55" s="2" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0.8</v>
+        <v>-2.7</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>普通坦克</t>
+          <t>绿兔子</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -2681,10 +2697,10 @@
         </is>
       </c>
       <c r="O55" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P55" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -2692,30 +2708,30 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="F56" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G56" s="2" t="n">
         <v>9</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>5</v>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J56" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J56" s="2" t="n">
-        <v>1.1</v>
-      </c>
       <c r="K56" s="2" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0.8</v>
+        <v>-2.7</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>绿皮怪1</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -2724,53 +2740,37 @@
         </is>
       </c>
       <c r="O56" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P56" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="D57" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E57" s="2" t="n">
-        <v>2003</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>4</v>
-      </c>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J57" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>泰森</t>
-        </is>
-      </c>
+        <v>-2.7</v>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="O57" s="2" t="n">
-        <v>3.2</v>
-      </c>
+      <c r="O57" s="2" t="inlineStr"/>
       <c r="P57" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -2778,30 +2778,30 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>2008</v>
+        <v>2001</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>21.6</v>
+        <v>22.1</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>-9.9</v>
+        <v>-6.8</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>黄鹿角</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -2810,10 +2810,10 @@
         </is>
       </c>
       <c r="O58" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P58" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -2821,30 +2821,30 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>2003</v>
+        <v>2028</v>
       </c>
       <c r="F59" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>21.6</v>
+        <v>22.1</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>-9.9</v>
+        <v>-6.8</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>黄犀牛</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="O59" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P59" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -2864,30 +2864,30 @@
         <v>18</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>2004</v>
+        <v>2026</v>
       </c>
       <c r="F60" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
       <c r="I60" s="2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>21.6</v>
+        <v>22.1</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>-9.9</v>
+        <v>-6.8</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>紫蝙蝠</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="O60" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P60" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -2907,42 +2907,42 @@
         <v>19</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>2003</v>
+        <v>2026</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>13.3</v>
+        <v>19</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>-3.3</v>
+        <v>-5</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>紫蝙蝠</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O61" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P61" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -2950,42 +2950,42 @@
         <v>19</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>13.3</v>
+        <v>19</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>-3.3</v>
+        <v>-5</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>黄鹿角</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O62" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P62" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -2999,20 +2999,20 @@
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="n">
-        <v>13.3</v>
+        <v>19</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>-3.3</v>
+        <v>-5</v>
       </c>
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr"/>
       <c r="P63" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -3020,30 +3020,30 @@
         <v>20</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>2003</v>
+        <v>2035</v>
       </c>
       <c r="F64" s="2" t="n">
         <v>8</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>20.7</v>
+        <v>19.5</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>-6.3</v>
+        <v>-3.7</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>绿蝾螈</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="O64" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P64" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -3063,30 +3063,30 @@
         <v>20</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>2004</v>
+        <v>2040</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>7</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>20.7</v>
+        <v>19.5</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>-6.3</v>
+        <v>-3.7</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>绿蘑菇</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -3095,10 +3095,10 @@
         </is>
       </c>
       <c r="O65" s="2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P65" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -3112,10 +3112,10 @@
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="n">
-        <v>20.7</v>
+        <v>19.5</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>-6.3</v>
+        <v>-3.7</v>
       </c>
       <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr"/>
       <c r="P66" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
